--- a/questionnaire_templates/030_home_dietetics_support_assessment--questionnaire_templates.xlsx
+++ b/questionnaire_templates/030_home_dietetics_support_assessment--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -949,8 +949,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -978,12 +978,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_1,_'text':_'5\'4"-8\'4"_(162-198_cm)',_'label':_'5\'4"-8\'4"_(162-198_cm)'}</t>
+          <t>5'4"-8'4"_(162-198_cm)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 1, 'text': '5\'4"-8\'4" (162-198 cm)', 'label': '5\'4"-8\'4" (162-198 cm)'}</t>
+          <t>5'4"-8'4" (162-198 cm)</t>
         </is>
       </c>
     </row>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_1,_'text':_'select_medication'}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 1, 'text': 'Select medication'}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_2,_'text':_'list_medication'}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 2, 'text': 'List medication'}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_1,_'text':_'food',_'label':_'food'}</t>
+          <t>food</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 1, 'text': 'Food', 'label': 'Food'}</t>
+          <t>Food</t>
         </is>
       </c>
     </row>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_2,_'text':_'environmental',_'label':_'environmental'}</t>
+          <t>environmental</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 2, 'text': 'Environmental', 'label': 'Environmental'}</t>
+          <t>Environmental</t>
         </is>
       </c>
     </row>
@@ -1080,12 +1080,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_3,_'text':_'medical',_'label':_'medical'}</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 3, 'text': 'Medical', 'label': 'Medical'}</t>
+          <t>Medical</t>
         </is>
       </c>
     </row>
@@ -1097,12 +1097,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_1,_'text':_'cardiovascular',_'label':_'cardiovascular'}</t>
+          <t>cardiovascular</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 1, 'text': 'Cardiovascular', 'label': 'Cardiovascular'}</t>
+          <t>Cardiovascular</t>
         </is>
       </c>
     </row>
@@ -1114,12 +1114,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_2,_'text':_'diabetes',_'label':_'diabetes'}</t>
+          <t>diabetes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 2, 'text': 'Diabetes', 'label': 'Diabetes'}</t>
+          <t>Diabetes</t>
         </is>
       </c>
     </row>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_3,_'text':_'digestive',_'label':_'digestive'}</t>
+          <t>digestive</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 3, 'text': 'Digestive', 'label': 'Digestive'}</t>
+          <t>Digestive</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_4,_'text':_'neurological',_'label':_'neurological'}</t>
+          <t>neurological</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 4, 'text': 'Neurological', 'label': 'Neurological'}</t>
+          <t>Neurological</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_5,_'text':_'respiratory',_'label':_'respiratory'}</t>
+          <t>respiratory</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 5, 'text': 'Respiratory', 'label': 'Respiratory'}</t>
+          <t>Respiratory</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_1,_'text':_'private',_'label':_'private'}</t>
+          <t>private</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 1, 'text': 'Private', 'label': 'Private'}</t>
+          <t>Private</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_1,_'text':_'employed',_'label':_'employed'}</t>
+          <t>employed</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 1, 'text': 'Employed', 'label': 'Employed'}</t>
+          <t>Employed</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_2,_'text':_'retiree',_'label':_'retiree'}</t>
+          <t>retiree</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 2, 'text': 'Retiree', 'label': 'Retiree'}</t>
+          <t>Retiree</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_3,_'text':_'unemployed',_'label':_'unemployed'}</t>
+          <t>unemployed</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 3, 'text': 'Unemployed', 'label': 'Unemployed'}</t>
+          <t>Unemployed</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_1,_'text':_'bachelor',_'label':_'bachelor'}</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 1, 'text': 'Bachelor', 'label': 'Bachelor'}</t>
+          <t>Bachelor</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_2,_'text':_'master',_'label':_'master'}</t>
+          <t>master</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 2, 'text': 'Master', 'label': 'Master'}</t>
+          <t>Master</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_3,_'text':_'doctoral',_'label':_'doctoral'}</t>
+          <t>doctoral</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 3, 'text': 'Doctoral', 'label': 'Doctoral'}</t>
+          <t>Doctoral</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_1,_'text':_'single',_'label':_'single'}</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 1, 'text': 'Single', 'label': 'Single'}</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_2,_'text':_'divorced',_'label':_'divorced'}</t>
+          <t>divorced</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 2, 'text': 'Divorced', 'label': 'Divorced'}</t>
+          <t>Divorced</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_3,_'text':_'married',_'label':_'married'}</t>
+          <t>married</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 3, 'text': 'Married', 'label': 'Married'}</t>
+          <t>Married</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_4,_'text':_'widowed',_'label':_'widowed'}</t>
+          <t>widowed</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 4, 'text': 'Widowed', 'label': 'Widowed'}</t>
+          <t>Widowed</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_1,_'text':_'low',_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 1, 'text': 'Low', 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_2,_'text':_'normal',_'label':_'normal'}</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 2, 'text': 'Normal', 'label': 'Normal'}</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_3,_'text':_'high',_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 3, 'text': 'High', 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
